--- a/Exp4_OpenStack/eda/results/lookahead/reward/tables/reward.xlsx
+++ b/Exp4_OpenStack/eda/results/lookahead/reward/tables/reward.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +999,523 @@
         <v>-0.1675749714188388</v>
       </c>
       <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>96</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.05741421568627453</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.227000612745098</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1089506740196078</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.05741421568627453</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.227000612745098</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1089506740196078</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.06771028821511017</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.06562500000000003</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.1989675245098039</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0723376225490194</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.06562500000000003</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.1989675245098039</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0723376225490194</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.09511815216909959</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>96</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02892156862745093</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.1343765318627452</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1865211397058823</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.02892156862745093</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.1343765318627452</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1865211397058823</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.03569750831605448</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1075367647058824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.06464460784313718</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2835998774509803</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1075367647058824</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.06464460784313718</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2835998774509803</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1196607715119267</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>96</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1188725490196079</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2807858455882353</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.04645526960784307</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.1188725490196079</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.2807858455882353</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.04645526960784307</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.1409467954902143</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>96</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.002267156862745067</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.1432092524509804</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1483930759803919</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.002267156862745067</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1432092524509804</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1483930759803919</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.003152559565113579</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2806372549019609</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.4104304534313725</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.1514537377450982</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.2806372549019609</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.4104304534313725</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.1514537377450982</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.4324013245480942</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3550857843137254</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.4779626225490195</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2389430147058824</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.3550857843137254</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.4779626225490195</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.2389430147058824</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.5875953837102122</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>96</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.1969362745098039</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.2930223651960783</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1017126225490195</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.1969362745098039</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.2930223651960783</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.1017126225490195</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.4163103566590478</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>96</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.2267156862745098</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.3306418504901961</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1196078431372549</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.2267156862745098</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.3306418504901961</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1196078431372549</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.4176920369689697</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>96</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.2452205882352941</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.3515364583333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.1424310661764707</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.2452205882352941</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.3515364583333333</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.1424310661764707</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4597984936333943</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1013,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,7 +1757,7 @@
         <v>0.1039186913009921</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6558960958334179</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
@@ -1336,7 +1853,7 @@
         <v>0.1736039180878427</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8680195904392135</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
@@ -1432,7 +1949,7 @@
         <v>0.09369944226191684</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6558960958334179</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
@@ -1816,7 +2333,7 @@
         <v>0.05255887759563913</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4204710207651131</v>
+        <v>0.6307065311476696</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -2008,7 +2525,7 @@
         <v>1.296626484288885e-07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.166963835859997e-06</v>
+        <v>2.333927671719993e-06</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2020,6 +2537,890 @@
       </c>
       <c r="AA10" t="n">
         <v>0.09637548294876909</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Q1+Q2</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>96</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.2452205882352941</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.3515364583333333</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1424310661764707</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.4597984936333943</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.2452205882352941</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.3515364583333333</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.1424310661764707</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.4597984936333943</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>-4.505086775608622</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.88776393428192e-05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0003020422294851072</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.533321860838485</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>96</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.2104166666666666</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.3250520833333333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.09994791666666683</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.3566379687252804</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.2104166666666666</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.3250520833333333</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.09994791666666683</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.3566379687252804</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>-3.494324185118408</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0007237360272864153</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01013230438200981</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5900007433834151</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>96</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.2800245098039215</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.3940104166666666</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.1740042892156863</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.5053061869711952</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2800245098039215</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.3940104166666666</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.1740042892156863</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.5053061869711952</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-4.950969287803286</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.197742542662394e-06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.436162322526069e-05</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5541679817585218</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WAI_SR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>96</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.07204861111111112</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.1858072916666667</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03993055555555555</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1298564981695496</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.07204861111111112</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1858072916666667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.03993055555555555</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1298564981695496</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.272328641200217</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.2063617950054993</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5548325430510183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CSQ8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CSQ8</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>96</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.00390625</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.1184895833333333</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1211263020833332</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.006471935047094176</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.00390625</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1184895833333333</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1211263020833332</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.006471935047094176</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.06341175405526459</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.9495718616989119</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6035675530695972</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MI_SAT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>96</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.05729166666666674</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.1996527777777779</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.08333333333333325</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.0813646202830854</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.05729166666666674</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.1996527777777779</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.08333333333333325</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.0813646202830854</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.7972072112354631</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.4273187110113473</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.704134874191466</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>96</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.2552083333333333</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.3697916666666667</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.140625</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.4441020838231807</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.2552083333333333</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.3697916666666667</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.140625</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.4441020838231807</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>-4.351293996294064</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.406999494841583e-05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0005110499242262375</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.5746614182403714</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>96</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.02013639520774775</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.04966040789213438</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.01030329159610311</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.1332248716341266</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.02013639520774775</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.04966040789213438</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.01030329159610311</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.1332248716341266</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.305331826205594</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1949324880157886</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1511459156293881</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0, ThL1B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MICI [lower better]</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>96</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.01426579891323212</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.001527825584693099</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.02748794288976819</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2204186194487082</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.01426579891323212</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.02748794288976819</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.001527825584693099</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.2204186194487082</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>2.159652589832157</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.03331700590412304</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.4331210767535996</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.06472138764371399</v>
       </c>
     </row>
   </sheetData>
@@ -2033,7 +3434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,6 +4438,870 @@
         <v>0.1836022780785235</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Q1+Q2</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>96</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.05741421568627453</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.227000612745098</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1089506740196078</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.06771028821511017</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.05741421568627453</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.227000612745098</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1089506740196078</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.06771028821511017</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.6634226258552202</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5086666242506367</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.8479393191160871</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>96</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2521354166666667</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.08642683280100168</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.075</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.2521354166666667</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.08642683280100168</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.8468065617891611</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.3992311266609516</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.8677860517310402</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>96</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.03982843137254901</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.2347120098039216</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1366574754901959</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.04225088457377925</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.03982843137254901</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.2347120098039216</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1366574754901959</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.04225088457377925</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.4139724335479531</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.6798274310231023</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.9426650299593111</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WAI_SR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>96</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.02690972222222221</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.1380425347222222</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1805989583333331</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.03437579891149174</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.02690972222222221</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1380425347222222</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1805989583333331</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.03437579891149174</v>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3368126673347046</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.7370010514061627</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.782810089490789</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CSQ8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CSQ8</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>96</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.1106770833333333</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1536783854166665</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.03164410191918914</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.1106770833333333</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1536783854166665</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.03164410191918914</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3100476122825571</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.7572038743252616</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6583638678239719</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MI_SAT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>96</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01215277777777778</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.1632378472222223</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1927083333333333</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01355631219761514</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.01215277777777778</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.1632378472222223</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1927083333333333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01355631219761514</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1328241907120991</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.8946133611480119</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.896466354611966</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>96</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.01041666666666667</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2057942708333333</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.171875</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.01089354418326224</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.01041666666666667</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2057942708333333</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.171875</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.01089354418326224</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.1067344989578248</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.9152246857106641</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.9562238415181454</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>96</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.001693180185827254</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.0460156317142216</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.05015219830398575</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.006838714126845742</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.001693180185827254</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.0460156317142216</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.05015219830398575</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.006838714126845742</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.06700544043014026</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.946718189418311</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.2475875075959944</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gpt4m</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GRPO: K5 - K0 @ base, ThL1B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GRPO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MICI [lower better]</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GRPO_LA5_ThL1B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>GRPO_LA0_ThL1B</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>96</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.02597563623274731</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.09640073838588134</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.04285674312335376</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.07666031535269727</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.02597563623274731</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.04285674312335376</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.09640073838588134</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.07666031535269727</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.7511146245398229</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.454440278179299</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.3388407171721002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
